--- a/4/turing/lab4/14/lab.xlsx
+++ b/4/turing/lab4/14/lab.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GUAP\guap\4\turing\lab4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stud\Documents\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555A7514-B197-4BBB-A4F1-C88E9DEA6270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A49819C-173B-49D9-B1D0-425CBEC10AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6435" yWindow="4065" windowWidth="12960" windowHeight="11415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14472" yWindow="1860" windowWidth="12180" windowHeight="12240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Мили" sheetId="1" r:id="rId1"/>
-    <sheet name="Мура" sheetId="2" r:id="rId2"/>
+    <sheet name="Мили" sheetId="3" r:id="rId1"/>
+    <sheet name="Мура" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
   <si>
     <t>a0</t>
   </si>
@@ -55,18 +55,12 @@
     <t>a7</t>
   </si>
   <si>
-    <t>a8</t>
-  </si>
-  <si>
     <t>a9</t>
   </si>
   <si>
     <t>a10</t>
   </si>
   <si>
-    <t>a11</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -76,45 +70,15 @@
     <t>a1/0</t>
   </si>
   <si>
-    <t>a7/B</t>
-  </si>
-  <si>
-    <t>a2/1</t>
-  </si>
-  <si>
-    <t>a3/0</t>
-  </si>
-  <si>
     <t>a0/1</t>
   </si>
   <si>
-    <t>a5/1</t>
-  </si>
-  <si>
-    <t>a8/1</t>
-  </si>
-  <si>
-    <t>a6/1</t>
-  </si>
-  <si>
     <t>a6/0</t>
   </si>
   <si>
-    <t>a0/0</t>
-  </si>
-  <si>
-    <t>a4/B</t>
-  </si>
-  <si>
-    <t>a9/0</t>
-  </si>
-  <si>
     <t>a10/1</t>
   </si>
   <si>
-    <t>a11/1</t>
-  </si>
-  <si>
     <t>a0'</t>
   </si>
   <si>
@@ -124,7 +88,34 @@
     <t>a12</t>
   </si>
   <si>
-    <t>-</t>
+    <t>a2/B</t>
+  </si>
+  <si>
+    <t>a3/1</t>
+  </si>
+  <si>
+    <t>a4/0</t>
+  </si>
+  <si>
+    <t>a7/1</t>
+  </si>
+  <si>
+    <t>a12/1</t>
+  </si>
+  <si>
+    <t>q12/1</t>
+  </si>
+  <si>
+    <t>q12/0</t>
+  </si>
+  <si>
+    <t>q0/1</t>
+  </si>
+  <si>
+    <t>a13</t>
+  </si>
+  <si>
+    <t>q0/0</t>
   </si>
 </sst>
 </file>
@@ -471,24 +462,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C662C7-399F-458F-8F3E-D2F922D75979}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="7" width="6" customWidth="1"/>
-    <col min="8" max="9" width="5.85546875" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -506,110 +494,86 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -620,27 +584,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7266769B-A765-4227-8E63-9AF6A61FD448}">
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D998ACCE-EE9B-4F05-8E98-DB8FE50D5F89}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="6.42578125" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" customWidth="1"/>
-    <col min="8" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="5.28515625" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" customWidth="1"/>
-    <col min="13" max="13" width="5.85546875" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="8" width="5.6640625" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" customWidth="1"/>
+    <col min="10" max="10" width="5.109375" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>0</v>
@@ -651,14 +611,14 @@
       <c r="D1" s="1">
         <v>0</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1">
         <v>1</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="H1" s="1">
         <v>1</v>
@@ -666,209 +626,132 @@
       <c r="I1" s="1">
         <v>0</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
+      <c r="J1" s="1">
+        <v>0</v>
       </c>
       <c r="K1" s="1">
         <v>1</v>
       </c>
       <c r="L1" s="1">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1">
         <v>1</v>
       </c>
-      <c r="N1" s="1">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/4/turing/lab4/14/lab.xlsx
+++ b/4/turing/lab4/14/lab.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stud\Documents\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GUAP\guap\4\turing\lab4\14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A49819C-173B-49D9-B1D0-425CBEC10AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5068BF84-FA29-4A1D-A75F-E4ACF381542F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14472" yWindow="1860" windowWidth="12180" windowHeight="12240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Мили" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
   <si>
     <t>a0</t>
   </si>
@@ -58,9 +58,6 @@
     <t>a9</t>
   </si>
   <si>
-    <t>a10</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -73,21 +70,12 @@
     <t>a0/1</t>
   </si>
   <si>
-    <t>a6/0</t>
-  </si>
-  <si>
-    <t>a10/1</t>
-  </si>
-  <si>
     <t>a0'</t>
   </si>
   <si>
     <t>a0''</t>
   </si>
   <si>
-    <t>a12</t>
-  </si>
-  <si>
     <t>a2/B</t>
   </si>
   <si>
@@ -100,22 +88,22 @@
     <t>a7/1</t>
   </si>
   <si>
-    <t>a12/1</t>
-  </si>
-  <si>
-    <t>q12/1</t>
-  </si>
-  <si>
-    <t>q12/0</t>
-  </si>
-  <si>
-    <t>q0/1</t>
-  </si>
-  <si>
-    <t>a13</t>
-  </si>
-  <si>
-    <t>q0/0</t>
+    <t>a8</t>
+  </si>
+  <si>
+    <t>a0/0</t>
+  </si>
+  <si>
+    <t>a5/0</t>
+  </si>
+  <si>
+    <t>a6/1</t>
+  </si>
+  <si>
+    <t>a8/1</t>
+  </si>
+  <si>
+    <t>a8/0</t>
   </si>
 </sst>
 </file>
@@ -464,19 +452,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C662C7-399F-458F-8F3E-D2F922D75979}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
-    <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -494,73 +482,73 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -570,10 +558,10 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -586,21 +574,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D998ACCE-EE9B-4F05-8E98-DB8FE50D5F89}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.44140625" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" customWidth="1"/>
-    <col min="7" max="8" width="5.6640625" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" customWidth="1"/>
-    <col min="11" max="11" width="5.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="8" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" customWidth="1"/>
+    <col min="11" max="11" width="5.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>0</v>
@@ -612,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1">
         <v>1</v>
@@ -636,105 +624,105 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -745,13 +733,13 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
